--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EFD4A9-0740-4E66-8B80-D6B354495B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47444F5E-5C51-4F11-99D0-0566EED561B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -192,7 +192,7 @@
             <v>609205</v>
           </cell>
           <cell r="N12">
-            <v>326130</v>
+            <v>340727</v>
           </cell>
         </row>
         <row r="13">
@@ -209,7 +209,7 @@
             <v>7.9169124537433147E-2</v>
           </cell>
           <cell r="N13">
-            <v>-0.46466296238540394</v>
+            <v>-0.44070222667246656</v>
           </cell>
         </row>
       </sheetData>
@@ -231,7 +231,7 @@
             <v>518112</v>
           </cell>
           <cell r="U9">
-            <v>269650</v>
+            <v>282168</v>
           </cell>
         </row>
         <row r="10">
@@ -251,7 +251,7 @@
             <v>0.15222801176886588</v>
           </cell>
           <cell r="U10">
-            <v>-0.47955268358964859</v>
+            <v>-0.45539188438021122</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>0.20193635458842044</v>
           </cell>
           <cell r="J7">
-            <v>-0.50791858146189195</v>
+            <v>-0.48429940171681263</v>
           </cell>
         </row>
         <row r="9">
@@ -290,7 +290,7 @@
             <v>461320</v>
           </cell>
           <cell r="J9">
-            <v>227007</v>
+            <v>237903</v>
           </cell>
         </row>
       </sheetData>
@@ -309,7 +309,7 @@
             <v>-0.37216510723499285</v>
           </cell>
           <cell r="J5">
-            <v>-7.9390389745791295E-2</v>
+            <v>-4.8511238539143235E-2</v>
           </cell>
         </row>
         <row r="7">
@@ -329,7 +329,7 @@
             <v>32611</v>
           </cell>
           <cell r="J7">
-            <v>30022</v>
+            <v>31029</v>
           </cell>
         </row>
       </sheetData>
@@ -348,7 +348,7 @@
             <v>88014</v>
           </cell>
           <cell r="I10">
-            <v>34652</v>
+            <v>36008</v>
           </cell>
         </row>
       </sheetData>
@@ -492,7 +492,7 @@
             <v>164217</v>
           </cell>
           <cell r="J15">
-            <v>116774</v>
+            <v>127321</v>
           </cell>
         </row>
       </sheetData>
@@ -514,7 +514,7 @@
             <v>31803</v>
           </cell>
           <cell r="J11">
-            <v>21596</v>
+            <v>23675</v>
           </cell>
         </row>
       </sheetData>
@@ -898,7 +898,7 @@
       </c>
       <c r="F3">
         <f>'[1]Total Unidades Mensuales'!N12</f>
-        <v>326130</v>
+        <v>340727</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -920,7 +920,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Unidades Mensuales'!N13</f>
-        <v>-0.46466296238540394</v>
+        <v>-0.44070222667246656</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F3">
         <f>'[1]Total Cremigurt Unidades'!U9</f>
-        <v>269650</v>
+        <v>282168</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Cremigurt Unidades'!U10</f>
-        <v>-0.47955268358964859</v>
+        <v>-0.45539188438021122</v>
       </c>
     </row>
   </sheetData>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F3">
         <f>'[1]150 gr'!J9</f>
-        <v>227007</v>
+        <v>237903</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]150 gr'!J7</f>
-        <v>-0.50791858146189195</v>
+        <v>-0.48429940171681263</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="F3">
         <f>'[1]700 gr'!J7</f>
-        <v>30022</v>
+        <v>31029</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]700 gr'!J5</f>
-        <v>-7.9390389745791295E-2</v>
+        <v>-4.8511238539143235E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="F3" s="2">
         <f>'[1]Linea Azul'!I10</f>
-        <v>34652</v>
+        <v>36008</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.60628990842365982</v>
+        <v>-0.59088326857090923</v>
       </c>
     </row>
   </sheetData>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Frutas!J15</f>
-        <v>116774</v>
+        <v>127321</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.2889043156311466</v>
+        <v>-0.22467832197640927</v>
       </c>
     </row>
   </sheetData>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Cremosillo!J11</f>
-        <v>21596</v>
+        <v>23675</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.32094456497814672</v>
+        <v>-0.25557337358110871</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47444F5E-5C51-4F11-99D0-0566EED561B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2BF8D1-5EFE-4DFB-B6F6-50CAE8241025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -159,11 +159,12 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sapori Produccion Mensual"/>
+      <sheetName val="Sapori Pruccion Mensual"/>
       <sheetName val="Comparativo vs Forecast"/>
       <sheetName val="Total Unidades Mensuales"/>
       <sheetName val="Total Cremigurt Unidades"/>
       <sheetName val="150 gr"/>
+      <sheetName val="Hoja3"/>
       <sheetName val="700 gr"/>
       <sheetName val="Linea Azul"/>
       <sheetName val="POWER"/>
@@ -192,7 +193,7 @@
             <v>609205</v>
           </cell>
           <cell r="N12">
-            <v>340727</v>
+            <v>394496</v>
           </cell>
         </row>
         <row r="13">
@@ -209,7 +210,7 @@
             <v>7.9169124537433147E-2</v>
           </cell>
           <cell r="N13">
-            <v>-0.44070222667246656</v>
+            <v>-0.35244129644372585</v>
           </cell>
         </row>
       </sheetData>
@@ -231,7 +232,7 @@
             <v>518112</v>
           </cell>
           <cell r="U9">
-            <v>282168</v>
+            <v>328319</v>
           </cell>
         </row>
         <row r="10">
@@ -251,7 +252,7 @@
             <v>0.15222801176886588</v>
           </cell>
           <cell r="U10">
-            <v>-0.45539188438021122</v>
+            <v>-0.36631654931752206</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +271,7 @@
             <v>0.20193635458842044</v>
           </cell>
           <cell r="J7">
-            <v>-0.48429940171681263</v>
+            <v>-0.39345573571490505</v>
           </cell>
         </row>
         <row r="9">
@@ -290,26 +291,18 @@
             <v>461320</v>
           </cell>
           <cell r="J9">
-            <v>237903</v>
+            <v>279811</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5">
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
         <row r="5">
-          <cell r="F5">
-            <v>-0.39088987917489776</v>
-          </cell>
-          <cell r="G5">
-            <v>0.44778821133612401</v>
-          </cell>
-          <cell r="H5">
-            <v>0.35297335312963973</v>
-          </cell>
           <cell r="I5">
             <v>-0.37216510723499285</v>
           </cell>
           <cell r="J5">
-            <v>-4.8511238539143235E-2</v>
+            <v>8.1598233724816782E-2</v>
           </cell>
         </row>
         <row r="7">
@@ -329,11 +322,11 @@
             <v>32611</v>
           </cell>
           <cell r="J7">
-            <v>31029</v>
+            <v>35272</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="6">
+      <sheetData sheetId="7">
         <row r="10">
           <cell r="E10">
             <v>27053</v>
@@ -348,11 +341,11 @@
             <v>88014</v>
           </cell>
           <cell r="I10">
-            <v>36008</v>
+            <v>59085</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7">
+      <sheetData sheetId="8">
         <row r="6">
           <cell r="C6">
             <v>22965</v>
@@ -450,7 +443,7 @@
             <v>19313</v>
           </cell>
           <cell r="H10">
-            <v>0</v>
+            <v>2358</v>
           </cell>
         </row>
         <row r="11">
@@ -474,7 +467,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8">
+      <sheetData sheetId="9">
         <row r="15">
           <cell r="E15">
             <v>222793</v>
@@ -492,11 +485,11 @@
             <v>164217</v>
           </cell>
           <cell r="J15">
-            <v>127321</v>
+            <v>143794</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9">
+      <sheetData sheetId="10">
         <row r="11">
           <cell r="E11">
             <v>19349</v>
@@ -514,11 +507,11 @@
             <v>31803</v>
           </cell>
           <cell r="J11">
-            <v>23675</v>
+            <v>28660</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10">
+      <sheetData sheetId="11">
         <row r="13">
           <cell r="E13">
             <v>18271</v>
@@ -536,7 +529,7 @@
             <v>52803</v>
           </cell>
           <cell r="J13">
-            <v>32496</v>
+            <v>34590</v>
           </cell>
         </row>
       </sheetData>
@@ -896,9 +889,9 @@
         <f>'[1]Total Unidades Mensuales'!M12</f>
         <v>609205</v>
       </c>
-      <c r="F3">
-        <f>'[1]Total Unidades Mensuales'!N12</f>
-        <v>340727</v>
+      <c r="F3" s="2">
+        <f>'[1]Total Unidades Mensuales'!$N$12</f>
+        <v>394496</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -920,7 +913,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Unidades Mensuales'!N13</f>
-        <v>-0.44070222667246656</v>
+        <v>-0.35244129644372585</v>
       </c>
     </row>
   </sheetData>
@@ -989,7 +982,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Gelatina!J13</f>
-        <v>32496</v>
+        <v>34590</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1012,7 +1005,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.38458042156695643</v>
+        <v>-0.34492358388727912</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +1074,7 @@
       </c>
       <c r="F3">
         <f>'[1]Total Cremigurt Unidades'!U9</f>
-        <v>282168</v>
+        <v>328319</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1107,7 +1100,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Cremigurt Unidades'!U10</f>
-        <v>-0.45539188438021122</v>
+        <v>-0.36631654931752206</v>
       </c>
     </row>
   </sheetData>
@@ -1176,7 +1169,7 @@
       </c>
       <c r="F3">
         <f>'[1]150 gr'!J9</f>
-        <v>237903</v>
+        <v>279811</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1199,7 +1192,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]150 gr'!J7</f>
-        <v>-0.48429940171681263</v>
+        <v>-0.39345573571490505</v>
       </c>
     </row>
   </sheetData>
@@ -1268,22 +1261,22 @@
       </c>
       <c r="F3">
         <f>'[1]700 gr'!J7</f>
-        <v>31029</v>
+        <v>35272</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3">
         <f>'[1]700 gr'!F5</f>
-        <v>-0.39088987917489776</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3">
         <f>'[1]700 gr'!G5</f>
-        <v>0.44778821133612401</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3">
         <f>'[1]700 gr'!H5</f>
-        <v>0.35297335312963973</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3">
         <f>'[1]700 gr'!I5</f>
@@ -1291,7 +1284,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]700 gr'!J5</f>
-        <v>-4.8511238539143235E-2</v>
+        <v>8.1598233724816782E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1359,7 +1352,7 @@
       </c>
       <c r="F3" s="2">
         <f>'[1]Linea Azul'!I10</f>
-        <v>36008</v>
+        <v>59085</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1379,7 +1372,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.59088326857090923</v>
+        <v>-0.3286863453541482</v>
       </c>
     </row>
   </sheetData>
@@ -1448,7 +1441,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]POWER!$H$6+[1]POWER!$H$8+[1]POWER!$H$10+[1]POWER!$H$11</f>
-        <v>26448</v>
+        <v>28806</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1471,7 +1464,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.70695061550564542</v>
+        <v>-0.68082348118026392</v>
       </c>
     </row>
   </sheetData>
@@ -1632,7 +1625,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Frutas!J15</f>
-        <v>127321</v>
+        <v>143794</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1655,7 +1648,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.22467832197640927</v>
+        <v>-0.12436593044569076</v>
       </c>
     </row>
   </sheetData>
@@ -1724,7 +1717,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Cremosillo!J11</f>
-        <v>23675</v>
+        <v>28660</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1747,7 +1740,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.25557337358110871</v>
+        <v>-9.8827154670942996E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2BF8D1-5EFE-4DFB-B6F6-50CAE8241025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C037D9-D268-4D85-B32E-96B2B2B5F50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -173,8 +173,8 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -193,7 +193,7 @@
             <v>609205</v>
           </cell>
           <cell r="N12">
-            <v>394496</v>
+            <v>408342</v>
           </cell>
         </row>
         <row r="13">
@@ -210,7 +210,7 @@
             <v>7.9169124537433147E-2</v>
           </cell>
           <cell r="N13">
-            <v>-0.35244129644372585</v>
+            <v>-0.32971331489400119</v>
           </cell>
         </row>
       </sheetData>
@@ -232,7 +232,7 @@
             <v>518112</v>
           </cell>
           <cell r="U9">
-            <v>328319</v>
+            <v>339252</v>
           </cell>
         </row>
         <row r="10">
@@ -252,7 +252,7 @@
             <v>0.15222801176886588</v>
           </cell>
           <cell r="U10">
-            <v>-0.36631654931752206</v>
+            <v>-0.34521493422271632</v>
           </cell>
         </row>
       </sheetData>
@@ -271,7 +271,7 @@
             <v>0.20193635458842044</v>
           </cell>
           <cell r="J7">
-            <v>-0.39345573571490505</v>
+            <v>-0.3875205930807249</v>
           </cell>
         </row>
         <row r="9">
@@ -291,11 +291,11 @@
             <v>461320</v>
           </cell>
           <cell r="J9">
-            <v>279811</v>
+            <v>282549</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">
@@ -443,7 +443,7 @@
             <v>19313</v>
           </cell>
           <cell r="H10">
-            <v>2358</v>
+            <v>5096</v>
           </cell>
         </row>
         <row r="11">
@@ -507,7 +507,7 @@
             <v>31803</v>
           </cell>
           <cell r="J11">
-            <v>28660</v>
+            <v>31033</v>
           </cell>
         </row>
       </sheetData>
@@ -891,7 +891,7 @@
       </c>
       <c r="F3" s="2">
         <f>'[1]Total Unidades Mensuales'!$N$12</f>
-        <v>394496</v>
+        <v>408342</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -913,7 +913,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Unidades Mensuales'!N13</f>
-        <v>-0.35244129644372585</v>
+        <v>-0.32971331489400119</v>
       </c>
     </row>
   </sheetData>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F3">
         <f>'[1]Total Cremigurt Unidades'!U9</f>
-        <v>328319</v>
+        <v>339252</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Cremigurt Unidades'!U10</f>
-        <v>-0.36631654931752206</v>
+        <v>-0.34521493422271632</v>
       </c>
     </row>
   </sheetData>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F3">
         <f>'[1]150 gr'!J9</f>
-        <v>279811</v>
+        <v>282549</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]150 gr'!J7</f>
-        <v>-0.39345573571490505</v>
+        <v>-0.3875205930807249</v>
       </c>
     </row>
   </sheetData>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]POWER!$H$6+[1]POWER!$H$8+[1]POWER!$H$10+[1]POWER!$H$11</f>
-        <v>28806</v>
+        <v>31544</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.68082348118026392</v>
+        <v>-0.65048586719260726</v>
       </c>
     </row>
   </sheetData>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Cremosillo!J11</f>
-        <v>28660</v>
+        <v>31033</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-9.8827154670942996E-2</v>
+        <v>-2.4211552369273338E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C037D9-D268-4D85-B32E-96B2B2B5F50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F81E716-8E06-47A9-8E72-E6F2853FF912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -193,7 +193,7 @@
             <v>609205</v>
           </cell>
           <cell r="N12">
-            <v>408342</v>
+            <v>414028</v>
           </cell>
         </row>
         <row r="13">
@@ -210,7 +210,7 @@
             <v>7.9169124537433147E-2</v>
           </cell>
           <cell r="N13">
-            <v>-0.32971331489400119</v>
+            <v>-0.32037983929875824</v>
           </cell>
         </row>
       </sheetData>
@@ -232,7 +232,7 @@
             <v>518112</v>
           </cell>
           <cell r="U9">
-            <v>339252</v>
+            <v>344938</v>
           </cell>
         </row>
         <row r="10">
@@ -252,7 +252,7 @@
             <v>0.15222801176886588</v>
           </cell>
           <cell r="U10">
-            <v>-0.34521493422271632</v>
+            <v>-0.33424047310234078</v>
           </cell>
         </row>
       </sheetData>
@@ -271,7 +271,7 @@
             <v>0.20193635458842044</v>
           </cell>
           <cell r="J7">
-            <v>-0.3875205930807249</v>
+            <v>-0.38077039798838119</v>
           </cell>
         </row>
         <row r="9">
@@ -291,7 +291,7 @@
             <v>461320</v>
           </cell>
           <cell r="J9">
-            <v>282549</v>
+            <v>285663</v>
           </cell>
         </row>
       </sheetData>
@@ -302,7 +302,7 @@
             <v>-0.37216510723499285</v>
           </cell>
           <cell r="J5">
-            <v>8.1598233724816782E-2</v>
+            <v>0.10048756554536813</v>
           </cell>
         </row>
         <row r="7">
@@ -322,7 +322,7 @@
             <v>32611</v>
           </cell>
           <cell r="J7">
-            <v>35272</v>
+            <v>35888</v>
           </cell>
         </row>
       </sheetData>
@@ -485,7 +485,7 @@
             <v>164217</v>
           </cell>
           <cell r="J15">
-            <v>143794</v>
+            <v>144874</v>
           </cell>
         </row>
       </sheetData>
@@ -891,7 +891,7 @@
       </c>
       <c r="F3" s="2">
         <f>'[1]Total Unidades Mensuales'!$N$12</f>
-        <v>408342</v>
+        <v>414028</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -913,7 +913,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Unidades Mensuales'!N13</f>
-        <v>-0.32971331489400119</v>
+        <v>-0.32037983929875824</v>
       </c>
     </row>
   </sheetData>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F3">
         <f>'[1]Total Cremigurt Unidades'!U9</f>
-        <v>339252</v>
+        <v>344938</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Cremigurt Unidades'!U10</f>
-        <v>-0.34521493422271632</v>
+        <v>-0.33424047310234078</v>
       </c>
     </row>
   </sheetData>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F3">
         <f>'[1]150 gr'!J9</f>
-        <v>282549</v>
+        <v>285663</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]150 gr'!J7</f>
-        <v>-0.3875205930807249</v>
+        <v>-0.38077039798838119</v>
       </c>
     </row>
   </sheetData>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="F3">
         <f>'[1]700 gr'!J7</f>
-        <v>35272</v>
+        <v>35888</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]700 gr'!J5</f>
-        <v>8.1598233724816782E-2</v>
+        <v>0.10048756554536813</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Frutas!J15</f>
-        <v>143794</v>
+        <v>144874</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.12436593044569076</v>
+        <v>-0.11778926664109075</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F81E716-8E06-47A9-8E72-E6F2853FF912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C40829-98A2-40C7-A0E1-BDCE1F86F2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -173,8 +173,8 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -193,7 +193,7 @@
             <v>609205</v>
           </cell>
           <cell r="N12">
-            <v>414028</v>
+            <v>433229</v>
           </cell>
         </row>
         <row r="13">
@@ -210,7 +210,7 @@
             <v>7.9169124537433147E-2</v>
           </cell>
           <cell r="N13">
-            <v>-0.32037983929875824</v>
+            <v>-0.28886171321640497</v>
           </cell>
         </row>
       </sheetData>
@@ -232,7 +232,7 @@
             <v>518112</v>
           </cell>
           <cell r="U9">
-            <v>344938</v>
+            <v>360256</v>
           </cell>
         </row>
         <row r="10">
@@ -252,7 +252,7 @@
             <v>0.15222801176886588</v>
           </cell>
           <cell r="U10">
-            <v>-0.33424047310234078</v>
+            <v>-0.30467543697115679</v>
           </cell>
         </row>
       </sheetData>
@@ -271,7 +271,7 @@
             <v>0.20193635458842044</v>
           </cell>
           <cell r="J7">
-            <v>-0.38077039798838119</v>
+            <v>-0.35585493800398854</v>
           </cell>
         </row>
         <row r="9">
@@ -291,11 +291,11 @@
             <v>461320</v>
           </cell>
           <cell r="J9">
-            <v>285663</v>
+            <v>297157</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">
@@ -485,7 +485,7 @@
             <v>164217</v>
           </cell>
           <cell r="J15">
-            <v>144874</v>
+            <v>156368</v>
           </cell>
         </row>
       </sheetData>
@@ -529,7 +529,7 @@
             <v>52803</v>
           </cell>
           <cell r="J13">
-            <v>34590</v>
+            <v>38453</v>
           </cell>
         </row>
       </sheetData>
@@ -891,7 +891,7 @@
       </c>
       <c r="F3" s="2">
         <f>'[1]Total Unidades Mensuales'!$N$12</f>
-        <v>414028</v>
+        <v>433229</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -913,7 +913,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Unidades Mensuales'!N13</f>
-        <v>-0.32037983929875824</v>
+        <v>-0.28886171321640497</v>
       </c>
     </row>
   </sheetData>
@@ -982,7 +982,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Gelatina!J13</f>
-        <v>34590</v>
+        <v>38453</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.34492358388727912</v>
+        <v>-0.27176486184497095</v>
       </c>
     </row>
   </sheetData>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F3">
         <f>'[1]Total Cremigurt Unidades'!U9</f>
-        <v>344938</v>
+        <v>360256</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Cremigurt Unidades'!U10</f>
-        <v>-0.33424047310234078</v>
+        <v>-0.30467543697115679</v>
       </c>
     </row>
   </sheetData>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F3">
         <f>'[1]150 gr'!J9</f>
-        <v>285663</v>
+        <v>297157</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]150 gr'!J7</f>
-        <v>-0.38077039798838119</v>
+        <v>-0.35585493800398854</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Frutas!J15</f>
-        <v>144874</v>
+        <v>156368</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.11778926664109075</v>
+        <v>-4.7796513150282854E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C40829-98A2-40C7-A0E1-BDCE1F86F2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DCD865-2952-420B-899F-E5FCCA3B6A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DCD865-2952-420B-899F-E5FCCA3B6A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2382EAFE-EBE7-4690-BCB9-1AA3C6F75F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2382EAFE-EBE7-4690-BCB9-1AA3C6F75F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268A3331-FC9A-4E8E-AC3F-03A2423FC2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -193,7 +193,7 @@
             <v>609205</v>
           </cell>
           <cell r="N12">
-            <v>433229</v>
+            <v>477514</v>
           </cell>
         </row>
         <row r="13">
@@ -210,7 +210,7 @@
             <v>7.9169124537433147E-2</v>
           </cell>
           <cell r="N13">
-            <v>-0.28886171321640497</v>
+            <v>-0.21616861319260347</v>
           </cell>
         </row>
       </sheetData>
@@ -232,7 +232,7 @@
             <v>518112</v>
           </cell>
           <cell r="U9">
-            <v>360256</v>
+            <v>393402</v>
           </cell>
         </row>
         <row r="10">
@@ -252,7 +252,7 @@
             <v>0.15222801176886588</v>
           </cell>
           <cell r="U10">
-            <v>-0.30467543697115679</v>
+            <v>-0.24070085232536595</v>
           </cell>
         </row>
       </sheetData>
@@ -271,7 +271,7 @@
             <v>0.20193635458842044</v>
           </cell>
           <cell r="J7">
-            <v>-0.35585493800398854</v>
+            <v>-0.29249544784531345</v>
           </cell>
         </row>
         <row r="9">
@@ -291,7 +291,7 @@
             <v>461320</v>
           </cell>
           <cell r="J9">
-            <v>297157</v>
+            <v>326386</v>
           </cell>
         </row>
       </sheetData>
@@ -302,7 +302,7 @@
             <v>-0.37216510723499285</v>
           </cell>
           <cell r="J5">
-            <v>0.10048756554536813</v>
+            <v>0.22060041090429611</v>
           </cell>
         </row>
         <row r="7">
@@ -322,7 +322,7 @@
             <v>32611</v>
           </cell>
           <cell r="J7">
-            <v>35888</v>
+            <v>39805</v>
           </cell>
         </row>
       </sheetData>
@@ -485,7 +485,7 @@
             <v>164217</v>
           </cell>
           <cell r="J15">
-            <v>156368</v>
+            <v>176146</v>
           </cell>
         </row>
       </sheetData>
@@ -507,7 +507,7 @@
             <v>31803</v>
           </cell>
           <cell r="J11">
-            <v>31033</v>
+            <v>39846</v>
           </cell>
         </row>
       </sheetData>
@@ -529,7 +529,7 @@
             <v>52803</v>
           </cell>
           <cell r="J13">
-            <v>38453</v>
+            <v>40258</v>
           </cell>
         </row>
       </sheetData>
@@ -891,7 +891,7 @@
       </c>
       <c r="F3" s="2">
         <f>'[1]Total Unidades Mensuales'!$N$12</f>
-        <v>433229</v>
+        <v>477514</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -913,7 +913,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Unidades Mensuales'!N13</f>
-        <v>-0.28886171321640497</v>
+        <v>-0.21616861319260347</v>
       </c>
     </row>
   </sheetData>
@@ -982,7 +982,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Gelatina!J13</f>
-        <v>38453</v>
+        <v>40258</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.27176486184497095</v>
+        <v>-0.23758119803799027</v>
       </c>
     </row>
   </sheetData>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F3">
         <f>'[1]Total Cremigurt Unidades'!U9</f>
-        <v>360256</v>
+        <v>393402</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Cremigurt Unidades'!U10</f>
-        <v>-0.30467543697115679</v>
+        <v>-0.24070085232536595</v>
       </c>
     </row>
   </sheetData>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F3">
         <f>'[1]150 gr'!J9</f>
-        <v>297157</v>
+        <v>326386</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]150 gr'!J7</f>
-        <v>-0.35585493800398854</v>
+        <v>-0.29249544784531345</v>
       </c>
     </row>
   </sheetData>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="F3">
         <f>'[1]700 gr'!J7</f>
-        <v>35888</v>
+        <v>39805</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]700 gr'!J5</f>
-        <v>0.10048756554536813</v>
+        <v>0.22060041090429611</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Frutas!J15</f>
-        <v>156368</v>
+        <v>176146</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-4.7796513150282854E-2</v>
+        <v>7.2641687523216231E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Cremosillo!J11</f>
-        <v>31033</v>
+        <v>39846</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-2.4211552369273338E-2</v>
+        <v>0.25290066974813696</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268A3331-FC9A-4E8E-AC3F-03A2423FC2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB7614A-488A-4D86-BBA9-835CC3E7A6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -173,8 +173,8 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -295,7 +295,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB7614A-488A-4D86-BBA9-835CC3E7A6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9874EBEF-9203-4B78-92E9-C08F85A3C833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -173,8 +173,8 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -193,7 +193,7 @@
             <v>609205</v>
           </cell>
           <cell r="N12">
-            <v>477514</v>
+            <v>518837</v>
           </cell>
         </row>
         <row r="13">
@@ -210,7 +210,7 @@
             <v>7.9169124537433147E-2</v>
           </cell>
           <cell r="N13">
-            <v>-0.21616861319260347</v>
+            <v>-0.14833758751159298</v>
           </cell>
         </row>
       </sheetData>
@@ -232,7 +232,7 @@
             <v>518112</v>
           </cell>
           <cell r="U9">
-            <v>393402</v>
+            <v>429574</v>
           </cell>
         </row>
         <row r="10">
@@ -252,7 +252,7 @@
             <v>0.15222801176886588</v>
           </cell>
           <cell r="U10">
-            <v>-0.24070085232536595</v>
+            <v>-0.17088583163485888</v>
           </cell>
         </row>
       </sheetData>
@@ -271,7 +271,7 @@
             <v>0.20193635458842044</v>
           </cell>
           <cell r="J7">
-            <v>-0.29249544784531345</v>
+            <v>-0.22600580941645712</v>
           </cell>
         </row>
         <row r="9">
@@ -291,18 +291,18 @@
             <v>461320</v>
           </cell>
           <cell r="J9">
-            <v>326386</v>
+            <v>357059</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">
             <v>-0.37216510723499285</v>
           </cell>
           <cell r="J5">
-            <v>0.22060041090429611</v>
+            <v>0.38922449480236732</v>
           </cell>
         </row>
         <row r="7">
@@ -322,7 +322,7 @@
             <v>32611</v>
           </cell>
           <cell r="J7">
-            <v>39805</v>
+            <v>45304</v>
           </cell>
         </row>
       </sheetData>
@@ -383,7 +383,7 @@
             <v>2122</v>
           </cell>
           <cell r="H7">
-            <v>1755</v>
+            <v>2340</v>
           </cell>
         </row>
         <row r="8">
@@ -403,7 +403,7 @@
             <v>26525</v>
           </cell>
           <cell r="H8">
-            <v>18230</v>
+            <v>21670</v>
           </cell>
         </row>
         <row r="9">
@@ -423,7 +423,7 @@
             <v>1814</v>
           </cell>
           <cell r="H9">
-            <v>2253</v>
+            <v>2832</v>
           </cell>
         </row>
         <row r="10">
@@ -485,7 +485,7 @@
             <v>164217</v>
           </cell>
           <cell r="J15">
-            <v>176146</v>
+            <v>194544</v>
           </cell>
         </row>
       </sheetData>
@@ -529,7 +529,7 @@
             <v>52803</v>
           </cell>
           <cell r="J13">
-            <v>40258</v>
+            <v>45389</v>
           </cell>
         </row>
       </sheetData>
@@ -891,7 +891,7 @@
       </c>
       <c r="F3" s="2">
         <f>'[1]Total Unidades Mensuales'!$N$12</f>
-        <v>477514</v>
+        <v>518837</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -913,7 +913,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Unidades Mensuales'!N13</f>
-        <v>-0.21616861319260347</v>
+        <v>-0.14833758751159298</v>
       </c>
     </row>
   </sheetData>
@@ -982,7 +982,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Gelatina!J13</f>
-        <v>40258</v>
+        <v>45389</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.23758119803799027</v>
+        <v>-0.14040868890025188</v>
       </c>
     </row>
   </sheetData>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F3">
         <f>'[1]Total Cremigurt Unidades'!U9</f>
-        <v>393402</v>
+        <v>429574</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]Total Cremigurt Unidades'!U10</f>
-        <v>-0.24070085232536595</v>
+        <v>-0.17088583163485888</v>
       </c>
     </row>
   </sheetData>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F3">
         <f>'[1]150 gr'!J9</f>
-        <v>326386</v>
+        <v>357059</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]150 gr'!J7</f>
-        <v>-0.29249544784531345</v>
+        <v>-0.22600580941645712</v>
       </c>
     </row>
   </sheetData>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="F3">
         <f>'[1]700 gr'!J7</f>
-        <v>39805</v>
+        <v>45304</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F4" s="3">
         <f>'[1]700 gr'!J5</f>
-        <v>0.22060041090429611</v>
+        <v>0.38922449480236732</v>
       </c>
     </row>
   </sheetData>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]POWER!$H$6+[1]POWER!$H$8+[1]POWER!$H$10+[1]POWER!$H$11</f>
-        <v>31544</v>
+        <v>34984</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.65048586719260726</v>
+        <v>-0.61236994603937911</v>
       </c>
     </row>
   </sheetData>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]POWER!$H$7+[1]POWER!$H$9</f>
-        <v>4008</v>
+        <v>5172</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8292682926829267E-2</v>
+        <v>0.31402439024390244</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="F3" s="2">
         <f>[1]Frutas!J15</f>
-        <v>176146</v>
+        <v>194544</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>7.2641687523216231E-2</v>
+        <v>0.18467637333528197</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407004EF-250E-4048-87DA-F28319D726CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8823BA16-7311-4122-A2E1-6C6725B08E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
   <sheets>
     <sheet name="Produccion Total Mensual" sheetId="1" r:id="rId1"/>
@@ -138,9 +138,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -161,6 +158,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -202,8 +202,14 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0">
+        <row r="12">
+          <cell r="J12">
+            <v>65869</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -263,6 +269,9 @@
           <cell r="U9">
             <v>429574</v>
           </cell>
+          <cell r="V9">
+            <v>55962</v>
+          </cell>
         </row>
         <row r="10">
           <cell r="P10">
@@ -303,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.89586874998249588</v>
+            <v>-0.8603732156310302</v>
           </cell>
         </row>
         <row r="9">
@@ -327,7 +336,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">
@@ -337,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.90886014479957622</v>
+            <v>-0.86519954087939255</v>
           </cell>
         </row>
         <row r="7">
@@ -519,7 +528,7 @@
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>0</v>
+            <v>4015</v>
           </cell>
         </row>
       </sheetData>
@@ -544,7 +553,7 @@
             <v>194544</v>
           </cell>
           <cell r="K15">
-            <v>33678</v>
+            <v>40857</v>
           </cell>
         </row>
       </sheetData>
@@ -569,7 +578,7 @@
             <v>39846</v>
           </cell>
           <cell r="K11">
-            <v>5312</v>
+            <v>8355</v>
           </cell>
         </row>
       </sheetData>
@@ -594,7 +603,7 @@
             <v>45389</v>
           </cell>
           <cell r="K13">
-            <v>0</v>
+            <v>1022</v>
           </cell>
         </row>
       </sheetData>
@@ -628,66 +637,39 @@
       <sheetName val="RESUMEN COP BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="D4">
-            <v>5312</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="24">
-          <cell r="C24">
-            <v>15906</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>37181</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="AD90">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="AD91">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="AJ101">
-            <v>47152</v>
+            <v>52352</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9">
         <row r="3">
           <cell r="C3">
-            <v>0</v>
+            <v>5692</v>
           </cell>
         </row>
         <row r="39">
           <cell r="G39">
-            <v>4129</v>
+            <v>9155</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -994,14 +976,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1022,7 +1004,7 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <v>46235</v>
       </c>
     </row>
@@ -1051,9 +1033,9 @@
         <f>'[1]Total Unidades Mensuales'!$N$12</f>
         <v>518837</v>
       </c>
-      <c r="G3" s="10">
-        <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AJ$101</f>
-        <v>47152</v>
+      <c r="G3" s="9">
+        <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
+        <v>65869</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1077,7 +1059,7 @@
         <f>'[1]Total Unidades Mensuales'!N13</f>
         <v>-0.14833758751159298</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1093,14 +1075,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1121,7 +1103,7 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>46235</v>
       </c>
     </row>
@@ -1152,7 +1134,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Gelatina!$K$13</f>
-        <v>0</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1179,7 +1161,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>-0.97748353125206544</v>
       </c>
     </row>
   </sheetData>
@@ -1196,14 +1178,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1224,7 +1206,7 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>46235</v>
       </c>
     </row>
@@ -1253,9 +1235,9 @@
         <f>'[1]Total Cremigurt Unidades'!U9</f>
         <v>429574</v>
       </c>
-      <c r="G3" s="7">
-        <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88+'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$90+'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$91</f>
-        <v>37181</v>
+      <c r="G3" s="6">
+        <f>'[1]Total Cremigurt Unidades'!$V$9</f>
+        <v>55962</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1283,9 +1265,9 @@
         <f>'[1]Total Cremigurt Unidades'!U10</f>
         <v>-0.17088583163485888</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.91344681009558304</v>
+        <v>-0.86972675255020093</v>
       </c>
     </row>
   </sheetData>
@@ -1302,14 +1284,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1330,7 +1312,7 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>46235</v>
       </c>
     </row>
@@ -1359,9 +1341,9 @@
         <f>'[1]150 gr'!J9</f>
         <v>357059</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>37181</v>
+        <v>52352</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1388,7 +1370,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.89586874998249588</v>
+        <v>-0.8603732156310302</v>
       </c>
     </row>
   </sheetData>
@@ -1405,14 +1387,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1433,7 +1415,7 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>46235</v>
       </c>
     </row>
@@ -1462,9 +1444,9 @@
         <f>'[1]700 gr'!J7</f>
         <v>45304</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>4129</v>
+        <v>9155</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1491,7 +1473,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.90886014479957622</v>
+        <v>-0.86519954087939255</v>
       </c>
     </row>
   </sheetData>
@@ -1508,14 +1490,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1536,7 +1518,7 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>46235</v>
       </c>
     </row>
@@ -1607,14 +1589,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1635,7 +1617,7 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="12">
         <v>46235</v>
       </c>
     </row>
@@ -1666,7 +1648,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>3503</v>
+        <v>7518</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1693,7 +1675,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.89986851131946033</v>
+        <v>-0.78510176080493943</v>
       </c>
     </row>
   </sheetData>
@@ -1710,14 +1692,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1738,7 +1720,7 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="12">
         <v>46235</v>
       </c>
     </row>
@@ -1813,14 +1795,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1841,7 +1823,7 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="12">
         <v>46235</v>
       </c>
     </row>
@@ -1872,7 +1854,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Frutas!$K$15</f>
-        <v>33678</v>
+        <v>40857</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1899,7 +1881,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.82688749074759438</v>
+        <v>-0.78998581297804094</v>
       </c>
     </row>
   </sheetData>
@@ -1916,14 +1898,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1944,7 +1926,7 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>46235</v>
       </c>
     </row>
@@ -1975,7 +1957,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Cremosillo!$K$11</f>
-        <v>5312</v>
+        <v>8355</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2002,7 +1984,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.86668674396426237</v>
+        <v>-0.7903177232344526</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8823BA16-7311-4122-A2E1-6C6725B08E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C146DE8-906A-4C7B-9766-D69EB3B8693C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
   <sheets>
     <sheet name="Produccion Total Mensual" sheetId="1" r:id="rId1"/>
@@ -205,11 +205,11 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>65869</v>
+            <v>85163</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>55962</v>
+            <v>72880</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.8603732156310302</v>
+            <v>-0.82638163440775891</v>
           </cell>
         </row>
         <row r="9">
@@ -336,7 +336,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.86519954087939255</v>
+            <v>-0.75966802048384252</v>
           </cell>
         </row>
         <row r="7">
@@ -553,7 +553,7 @@
             <v>194544</v>
           </cell>
           <cell r="K15">
-            <v>40857</v>
+            <v>51825</v>
           </cell>
         </row>
       </sheetData>
@@ -578,7 +578,7 @@
             <v>39846</v>
           </cell>
           <cell r="K11">
-            <v>8355</v>
+            <v>10440</v>
           </cell>
         </row>
       </sheetData>
@@ -637,39 +637,34 @@
       <sheetName val="RESUMEN COP BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>52352</v>
+            <v>61992</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="8"/>
       <sheetData sheetId="9">
-        <row r="3">
-          <cell r="C3">
-            <v>5692</v>
-          </cell>
-        </row>
         <row r="39">
           <cell r="G39">
-            <v>9155</v>
+            <v>10888</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1035,7 +1030,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>65869</v>
+        <v>85163</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1237,7 +1232,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>55962</v>
+        <v>72880</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1267,7 +1262,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.86972675255020093</v>
+        <v>-0.83034354965617097</v>
       </c>
     </row>
   </sheetData>
@@ -1343,7 +1338,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>52352</v>
+        <v>61992</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1370,7 +1365,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.8603732156310302</v>
+        <v>-0.82638163440775891</v>
       </c>
     </row>
   </sheetData>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>9155</v>
+        <v>10888</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1473,7 +1468,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.86519954087939255</v>
+        <v>-0.75966802048384252</v>
       </c>
     </row>
   </sheetData>
@@ -1854,7 +1849,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Frutas!$K$15</f>
-        <v>40857</v>
+        <v>51825</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1881,7 +1876,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.78998581297804094</v>
+        <v>-0.73360782136688873</v>
       </c>
     </row>
   </sheetData>
@@ -1957,7 +1952,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Cremosillo!$K$11</f>
-        <v>8355</v>
+        <v>10440</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1984,7 +1979,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.7903177232344526</v>
+        <v>-0.73799126637554591</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C146DE8-906A-4C7B-9766-D69EB3B8693C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8F391D-CF12-498C-98AF-81A2CC84D25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,11 +205,11 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>85163</v>
+            <v>85351</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>72880</v>
+            <v>73068</v>
           </cell>
         </row>
         <row r="10">
@@ -336,7 +336,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.75966802048384252</v>
+            <v>-0.75551827653187353</v>
           </cell>
         </row>
         <row r="7">
@@ -553,7 +553,7 @@
             <v>194544</v>
           </cell>
           <cell r="K15">
-            <v>51825</v>
+            <v>52013</v>
           </cell>
         </row>
       </sheetData>
@@ -637,8 +637,20 @@
       <sheetName val="RESUMEN COP BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="D4">
+            <v>10440</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="24">
+          <cell r="C24">
+            <v>21928</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
@@ -655,7 +667,7 @@
       <sheetData sheetId="9">
         <row r="39">
           <cell r="G39">
-            <v>10888</v>
+            <v>11076</v>
           </cell>
         </row>
       </sheetData>
@@ -1030,7 +1042,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>85163</v>
+        <v>85351</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1232,7 +1244,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>72880</v>
+        <v>73068</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1262,7 +1274,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.83034354965617097</v>
+        <v>-0.82990590678206777</v>
       </c>
     </row>
   </sheetData>
@@ -1441,7 +1453,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>10888</v>
+        <v>11076</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1468,7 +1480,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.75966802048384252</v>
+        <v>-0.75551827653187353</v>
       </c>
     </row>
   </sheetData>
@@ -1849,7 +1861,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Frutas!$K$15</f>
-        <v>51825</v>
+        <v>52013</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1876,7 +1888,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.73360782136688873</v>
+        <v>-0.73264145900156263</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8F391D-CF12-498C-98AF-81A2CC84D25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E11AB8A-2A7A-460A-8BF5-F431FE5869B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,11 +205,11 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>85351</v>
+            <v>131621</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>73068</v>
+            <v>118445</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.82638163440775891</v>
+            <v>-0.71113457439806871</v>
           </cell>
         </row>
         <row r="9">
@@ -336,7 +336,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.75551827653187353</v>
+            <v>-0.66221525693095529</v>
           </cell>
         </row>
         <row r="7">
@@ -388,7 +388,7 @@
             <v>59085</v>
           </cell>
           <cell r="J10">
-            <v>0</v>
+            <v>15792</v>
           </cell>
         </row>
       </sheetData>
@@ -413,7 +413,7 @@
             <v>8218</v>
           </cell>
           <cell r="I6">
-            <v>0</v>
+            <v>3937</v>
           </cell>
         </row>
         <row r="7">
@@ -436,7 +436,7 @@
             <v>2340</v>
           </cell>
           <cell r="I7">
-            <v>0</v>
+            <v>482</v>
           </cell>
         </row>
         <row r="8">
@@ -459,7 +459,7 @@
             <v>21670</v>
           </cell>
           <cell r="I8">
-            <v>3503</v>
+            <v>7207</v>
           </cell>
         </row>
         <row r="9">
@@ -482,7 +482,7 @@
             <v>2832</v>
           </cell>
           <cell r="I9">
-            <v>464</v>
+            <v>968</v>
           </cell>
         </row>
         <row r="10">
@@ -505,7 +505,7 @@
             <v>5096</v>
           </cell>
           <cell r="I10">
-            <v>0</v>
+            <v>1296</v>
           </cell>
         </row>
         <row r="11">
@@ -528,7 +528,7 @@
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>4015</v>
+            <v>6025</v>
           </cell>
         </row>
       </sheetData>
@@ -553,7 +553,7 @@
             <v>194544</v>
           </cell>
           <cell r="K15">
-            <v>52013</v>
+            <v>56032</v>
           </cell>
         </row>
       </sheetData>
@@ -603,7 +603,7 @@
             <v>45389</v>
           </cell>
           <cell r="K13">
-            <v>1022</v>
+            <v>1776</v>
           </cell>
         </row>
       </sheetData>
@@ -637,20 +637,8 @@
       <sheetName val="RESUMEN COP BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="D4">
-            <v>10440</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="24">
-          <cell r="C24">
-            <v>21928</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
@@ -659,7 +647,7 @@
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>61992</v>
+            <v>103142</v>
           </cell>
         </row>
       </sheetData>
@@ -667,7 +655,7 @@
       <sheetData sheetId="9">
         <row r="39">
           <cell r="G39">
-            <v>11076</v>
+            <v>15303</v>
           </cell>
         </row>
       </sheetData>
@@ -1042,7 +1030,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>85351</v>
+        <v>131621</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1141,7 +1129,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Gelatina!$K$13</f>
-        <v>1022</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1168,7 +1156,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.97748353125206544</v>
+        <v>-0.96087157681376545</v>
       </c>
     </row>
   </sheetData>
@@ -1244,7 +1232,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>73068</v>
+        <v>118445</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1274,7 +1262,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.82990590678206777</v>
+        <v>-0.72427334987685477</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1338,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>61992</v>
+        <v>103142</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1377,7 +1365,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.82638163440775891</v>
+        <v>-0.71113457439806871</v>
       </c>
     </row>
   </sheetData>
@@ -1453,7 +1441,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>11076</v>
+        <v>15303</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1480,7 +1468,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.75551827653187353</v>
+        <v>-0.66221525693095529</v>
       </c>
     </row>
   </sheetData>
@@ -1555,7 +1543,7 @@
       </c>
       <c r="G3" s="2">
         <f>'[1]Linea Azul'!$J$10</f>
-        <v>0</v>
+        <v>15792</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1579,7 +1567,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>-0.73272404163493277</v>
       </c>
     </row>
   </sheetData>
@@ -1655,7 +1643,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>7518</v>
+        <v>18465</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1682,7 +1670,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.78510176080493943</v>
+        <v>-0.4721872856162817</v>
       </c>
     </row>
   </sheetData>
@@ -1758,7 +1746,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$7+[1]POWER!$I$9</f>
-        <v>464</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1785,7 +1773,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.91028615622583142</v>
+        <v>-0.7196442382057231</v>
       </c>
     </row>
   </sheetData>
@@ -1861,7 +1849,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Frutas!$K$15</f>
-        <v>52013</v>
+        <v>56032</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1888,7 +1876,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.73264145900156263</v>
+        <v>-0.71198289333004361</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E11AB8A-2A7A-460A-8BF5-F431FE5869B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F2A55E-14B8-45B5-AEAA-2689071C2E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -209,7 +209,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -336,7 +336,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">
@@ -637,13 +637,25 @@
       <sheetName val="RESUMEN COP BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="D4">
+            <v>10440</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="24">
+          <cell r="C24">
+            <v>21928</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
@@ -651,20 +663,25 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9">
+        <row r="3">
+          <cell r="C3">
+            <v>7568</v>
+          </cell>
+        </row>
         <row r="39">
           <cell r="G39">
             <v>15303</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/Historico_Produccion_CREMIGURT.xlsx
+++ b/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F2A55E-14B8-45B5-AEAA-2689071C2E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D6292F-56EC-4514-8DAF-7793247EFC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,7 +205,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>131621</v>
+            <v>160673</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>118445</v>
+            <v>274103</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.71113457439806871</v>
+            <v>-0.63861154599099867</v>
           </cell>
         </row>
         <row r="9">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.66221525693095529</v>
+            <v>-0.64619018188239452</v>
           </cell>
         </row>
         <row r="7">
@@ -388,7 +388,7 @@
             <v>59085</v>
           </cell>
           <cell r="J10">
-            <v>15792</v>
+            <v>18792</v>
           </cell>
         </row>
       </sheetData>
@@ -436,7 +436,7 @@
             <v>2340</v>
           </cell>
           <cell r="I7">
-            <v>482</v>
+            <v>855</v>
           </cell>
         </row>
         <row r="8">
@@ -482,7 +482,7 @@
             <v>2832</v>
           </cell>
           <cell r="I9">
-            <v>968</v>
+            <v>1321</v>
           </cell>
         </row>
         <row r="10">
@@ -505,7 +505,7 @@
             <v>5096</v>
           </cell>
           <cell r="I10">
-            <v>1296</v>
+            <v>2032</v>
           </cell>
         </row>
         <row r="11">
@@ -534,26 +534,8 @@
       </sheetData>
       <sheetData sheetId="9">
         <row r="15">
-          <cell r="E15">
-            <v>222793</v>
-          </cell>
-          <cell r="F15">
-            <v>98244</v>
-          </cell>
-          <cell r="G15">
-            <v>173801</v>
-          </cell>
-          <cell r="H15">
-            <v>192306</v>
-          </cell>
-          <cell r="I15">
-            <v>164217</v>
-          </cell>
-          <cell r="J15">
-            <v>194544</v>
-          </cell>
           <cell r="K15">
-            <v>56032</v>
+            <v>6010</v>
           </cell>
         </row>
       </sheetData>
@@ -578,7 +560,7 @@
             <v>39846</v>
           </cell>
           <cell r="K11">
-            <v>10440</v>
+            <v>12871</v>
           </cell>
         </row>
       </sheetData>
@@ -637,51 +619,34 @@
       <sheetName val="RESUMEN COP BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="D4">
-            <v>10440</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="24">
-          <cell r="C24">
-            <v>21928</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>103142</v>
+            <v>129037</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="8"/>
       <sheetData sheetId="9">
-        <row r="3">
-          <cell r="C3">
-            <v>7568</v>
-          </cell>
-        </row>
         <row r="39">
           <cell r="G39">
-            <v>15303</v>
+            <v>16029</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1047,7 +1012,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>131621</v>
+        <v>160673</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1249,7 +1214,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>118445</v>
+        <v>274103</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1279,7 +1244,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.72427334987685477</v>
+        <v>-0.36191901744518989</v>
       </c>
     </row>
   </sheetData>
@@ -1355,7 +1320,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>103142</v>
+        <v>129037</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1382,7 +1347,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.71113457439806871</v>
+        <v>-0.63861154599099867</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1423,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>15303</v>
+        <v>16029</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1485,7 +1450,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.66221525693095529</v>
+        <v>-0.64619018188239452</v>
       </c>
     </row>
   </sheetData>
@@ -1560,7 +1525,7 @@
       </c>
       <c r="G3" s="2">
         <f>'[1]Linea Azul'!$J$10</f>
-        <v>15792</v>
+        <v>18792</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1584,7 +1549,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.73272404163493277</v>
+        <v>-0.68194973343488197</v>
       </c>
     </row>
   </sheetData>
@@ -1660,7 +1625,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>18465</v>
+        <v>19201</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1687,7 +1652,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.4721872856162817</v>
+        <v>-0.4511490967299337</v>
       </c>
     </row>
   </sheetData>
@@ -1763,7 +1728,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$7+[1]POWER!$I$9</f>
-        <v>1450</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1790,7 +1755,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.7196442382057231</v>
+        <v>-0.57927300850734731</v>
       </c>
     </row>
   </sheetData>
@@ -1842,58 +1807,58 @@
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f>[1]Frutas!E15</f>
-        <v>222793</v>
+        <v>0</v>
       </c>
       <c r="B3" s="2">
         <f>[1]Frutas!F15</f>
-        <v>98244</v>
+        <v>0</v>
       </c>
       <c r="C3" s="2">
         <f>[1]Frutas!G15</f>
-        <v>173801</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
         <f>[1]Frutas!H15</f>
-        <v>192306</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2">
         <f>[1]Frutas!I15</f>
-        <v>164217</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
         <f>[1]Frutas!J15</f>
-        <v>194544</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
         <f>[1]Frutas!$K$15</f>
-        <v>56032</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="4">
+      <c r="B4" s="4" t="e">
         <f>(B3-A3)/A3</f>
-        <v>-0.55903461957960976</v>
-      </c>
-      <c r="C4" s="4">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C4" s="4" t="e">
         <f>(C3-B3)/B3</f>
-        <v>0.76907495623142386</v>
-      </c>
-      <c r="D4" s="4">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D4" s="4" t="e">
         <f t="shared" ref="D4:G4" si="0">(D3-C3)/C3</f>
-        <v>0.10647234480814265</v>
-      </c>
-      <c r="E4" s="4">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E4" s="4" t="e">
         <f t="shared" si="0"/>
-        <v>-0.14606408536395121</v>
-      </c>
-      <c r="F4" s="4">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F4" s="4" t="e">
         <f t="shared" si="0"/>
-        <v>0.18467637333528197</v>
-      </c>
-      <c r="G4" s="4">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G4" s="4" t="e">
         <f t="shared" si="0"/>
-        <v>-0.71198289333004361</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
@@ -1969,7 +1934,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Cremosillo!$K$11</f>
-        <v>10440</v>
+        <v>12871</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1996,7 +1961,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.73799126637554591</v>
+        <v>-0.67698137830647998</v>
       </c>
     </row>
   </sheetData>
